--- a/Analysis/tables/C4_robustness_by_region.xlsx
+++ b/Analysis/tables/C4_robustness_by_region.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,22 +444,37 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>toxicity_score_OR</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>leadership_score_coef</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>leadership_score_p</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>leadership_score_OR</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>toxicity_x_leadership_coef</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>toxicity_x_leadership_p</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>toxicity_x_leadership_OR</t>
         </is>
       </c>
     </row>
@@ -473,25 +488,34 @@
         <v>2435</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8032</v>
+        <v>0.824</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0521</v>
+        <v>0.0336</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6354</v>
+        <v>0.7729</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2241</v>
+        <v>1.0341</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008</v>
+        <v>0.2425</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0308</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5385</v>
+        <v>1.2744</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0.0435</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.9574</v>
       </c>
     </row>
     <row r="3">
@@ -504,25 +528,34 @@
         <v>2427</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8335</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.233</v>
+        <v>0.2713</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0549</v>
+        <v>0.0323</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1934</v>
+        <v>1.3116</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0247</v>
+        <v>0.2324</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.06950000000000001</v>
+        <v>0.0137</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1481</v>
+        <v>1.2617</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-0.0136</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.8083</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.9865</v>
       </c>
     </row>
     <row r="4">
@@ -535,25 +568,34 @@
         <v>2469</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7562</v>
+        <v>0.7782</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.062</v>
+        <v>-0.0375</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5026</v>
+        <v>0.6948</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2274</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="G4" t="n">
+        <v>0.2743</v>
+      </c>
+      <c r="H4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="n">
-        <v>-0.0332</v>
-      </c>
       <c r="I4" t="n">
-        <v>0.4461</v>
+        <v>1.3156</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0.0119</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.7969000000000001</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.9882</v>
       </c>
     </row>
     <row r="5">
@@ -566,25 +608,34 @@
         <v>2429</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7709</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0229</v>
+        <v>0.0445</v>
       </c>
       <c r="E5" t="n">
-        <v>0.848</v>
+        <v>0.7301</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3346</v>
+        <v>1.0455</v>
       </c>
       <c r="G5" t="n">
+        <v>0.3784</v>
+      </c>
+      <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="n">
-        <v>0.0137</v>
-      </c>
       <c r="I5" t="n">
-        <v>0.8495</v>
+        <v>1.46</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0519</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.4975</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.0532</v>
       </c>
     </row>
   </sheetData>
